--- a/pims/audit_checklist.xlsx
+++ b/pims/audit_checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://auditcopty-my.sharepoint.com/personal/alan_richardson_auditco_com/Documents/_RPD/_SSA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanRichardson\gatekeeper\pims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{EB7C5978-6ED6-4971-85A0-EA37ADEC4CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15E636C9-4293-447D-A141-C1AA3E7BB4B2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810251A2-55FA-4248-B8C6-FC3136757945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35490" yWindow="-2910" windowWidth="21645" windowHeight="14235" activeTab="1" xr2:uid="{91678ABD-00CB-4CA9-BCA2-78B54436A12B}"/>
+    <workbookView xWindow="30405" yWindow="-2970" windowWidth="21690" windowHeight="14235" activeTab="1" xr2:uid="{91678ABD-00CB-4CA9-BCA2-78B54436A12B}"/>
   </bookViews>
   <sheets>
     <sheet name="&lt;$250K_inspection_checklist" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="195">
   <si>
     <t>Category</t>
   </si>
@@ -603,6 +603,9 @@
   </si>
   <si>
     <t>Verify Site Safety Management Plan is available and accessible</t>
+  </si>
+  <si>
+    <t>01. Planning and Risk Management (Project Value &gt;$250K)</t>
   </si>
 </sst>
 </file>
@@ -1086,8 +1089,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1465,1082 +1471,1087 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4877856-2D65-44AD-90FE-3CB5F33D296A}">
   <dimension ref="A1:C98"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="46.5546875" customWidth="1"/>
+    <col min="3" max="3" width="36.21875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="12" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="13" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="15" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="16" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="19" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="20" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="22" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="23" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="24" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="25" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="26" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="27" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="28" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="29" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="30" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="31" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="32" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="33" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="34" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="35" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="37" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="38" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="39" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="40" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="41" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="42" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="43" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="44" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="45" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="46" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="47" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="48" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="49" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="50" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="51" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="53" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="54" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="55" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="56" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="57" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="58" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="59" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="60" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="61" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="62" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="63" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="64" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="65" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="66" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="67" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="68" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="69" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="70" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="71" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="72" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="73" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="74" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="75" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="76" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="77" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="78" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="79" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="80" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="81" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="82" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="83" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="84" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="85" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="86" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="87" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="88" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="89" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="90" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="91" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="92" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="93" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="94" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    <row r="95" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="96" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+    <row r="97" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+    <row r="98" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="1" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2554,1084 +2565,1085 @@
   <dimension ref="A1:C98"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="55.109375" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
+    <col min="2" max="3" width="36.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="6" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="10" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="11" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="12" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
+    <row r="13" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="15" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="18" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="19" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="20" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="22" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" t="s">
+    <row r="23" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="24" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="25" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" t="s">
+    <row r="26" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" t="s">
+    <row r="27" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" t="s">
+    <row r="28" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" t="s">
+    <row r="29" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="30" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" t="s">
+    <row r="31" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="32" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="33" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="34" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="35" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="37" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="38" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="39" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="40" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="41" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="42" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="43" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="44" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="45" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="46" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="47" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="48" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="49" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="50" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="51" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="53" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="54" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="55" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="56" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="57" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="58" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="59" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="60" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="61" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="62" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="63" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="64" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="65" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="66" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="67" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="68" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="69" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="70" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="71" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="72" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="73" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="74" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="75" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="76" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="77" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="78" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="79" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="80" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="81" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="82" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="83" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="84" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="85" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="86" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="87" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="88" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="89" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="90" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="91" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="92" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="93" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="94" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    <row r="95" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="96" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+    <row r="97" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+    <row r="98" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="1" t="s">
         <v>191</v>
       </c>
     </row>

--- a/pims/audit_checklist.xlsx
+++ b/pims/audit_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanRichardson\gatekeeper\pims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810251A2-55FA-4248-B8C6-FC3136757945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386F8446-28E9-425A-B002-422A16D7CE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30405" yWindow="-2970" windowWidth="21690" windowHeight="14235" activeTab="1" xr2:uid="{91678ABD-00CB-4CA9-BCA2-78B54436A12B}"/>
+    <workbookView xWindow="8760" yWindow="1032" windowWidth="14376" windowHeight="12180" activeTab="1" xr2:uid="{91678ABD-00CB-4CA9-BCA2-78B54436A12B}"/>
   </bookViews>
   <sheets>
     <sheet name="&lt;$250K_inspection_checklist" sheetId="2" r:id="rId1"/>
@@ -2591,7 +2591,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>194</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>194</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>194</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>194</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>194</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>194</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>194</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>194</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>194</v>
       </c>
